--- a/data/manual_flags.xlsx
+++ b/data/manual_flags.xlsx
@@ -19823,7 +19823,7 @@
       </c>
       <c r="P294" s="5" t="inlineStr">
         <is>
-          <t>Ryan flag (Day 5): FFP / financial pressure — public must-sell</t>
+          <t>Manual flag: FFP / financial pressure — public must-sell</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr"/>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="P306" s="5" t="inlineStr">
         <is>
-          <t>Ryan flag (Day 5): FFP / financial pressure — public must-sell</t>
+          <t>Manual flag: FFP / financial pressure — public must-sell</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr"/>
